--- a/연구코드/results/feature_selection/sinchon/step2_vif.xlsx
+++ b/연구코드/results/feature_selection/sinchon/step2_vif.xlsx
@@ -536,7 +536,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>159.0133372106835</v>
+        <v>159.0133372106722</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>148.7113016225247</v>
+        <v>148.7113016225222</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -592,7 +592,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>73.9592654958339</v>
+        <v>73.95926549583329</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -608,7 +608,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>58.59776609909621</v>
+        <v>58.59776609909582</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -624,7 +624,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>52.91039906801216</v>
+        <v>52.91039906801186</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -632,7 +632,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>33.03756809422134</v>
+        <v>33.03756809422122</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -640,7 +640,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>31.39750788081958</v>
+        <v>31.39750788081925</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -696,7 +696,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>13.43059426558227</v>
+        <v>13.43059426558223</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -728,7 +728,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>10.29544073589627</v>
+        <v>10.29544073589626</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -744,7 +744,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>8.184992379074702</v>
+        <v>8.184992379074686</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -752,7 +752,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>6.936780389651926</v>
+        <v>6.936780389651807</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -768,7 +768,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>6.179403118007395</v>
+        <v>6.179403118007353</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -784,7 +784,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>3.605153515701735</v>
+        <v>3.605153515701726</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -792,7 +792,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>3.555278190690234</v>
+        <v>3.555278190690232</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/feature_selection/sinchon/step2_vif.xlsx
+++ b/연구코드/results/feature_selection/sinchon/step2_vif.xlsx
@@ -536,7 +536,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>159.0133372106722</v>
+        <v>159.0133372106835</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>148.7113016225222</v>
+        <v>148.7113016225247</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -592,7 +592,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>73.95926549583329</v>
+        <v>73.9592654958339</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -608,7 +608,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>58.59776609909582</v>
+        <v>58.59776609909621</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -624,7 +624,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>52.91039906801186</v>
+        <v>52.91039906801216</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -632,7 +632,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>33.03756809422122</v>
+        <v>33.03756809422134</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -640,7 +640,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>31.39750788081925</v>
+        <v>31.39750788081958</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -696,7 +696,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>13.43059426558223</v>
+        <v>13.43059426558227</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -728,7 +728,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>10.29544073589626</v>
+        <v>10.29544073589627</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -744,7 +744,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>8.184992379074686</v>
+        <v>8.184992379074702</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -752,7 +752,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>6.936780389651807</v>
+        <v>6.936780389651926</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -768,7 +768,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>6.179403118007353</v>
+        <v>6.179403118007395</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -784,7 +784,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>3.605153515701726</v>
+        <v>3.605153515701735</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -792,7 +792,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>3.555278190690232</v>
+        <v>3.555278190690234</v>
       </c>
     </row>
   </sheetData>
